--- a/data/gravel/Quirk SUPRACHUB 2025.xlsx
+++ b/data/gravel/Quirk SUPRACHUB 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B27E10-8E0A-6141-AEB1-62AA2B0DB6F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB21CDAC-295E-4647-8FF2-D21332506096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2720" yWindow="720" windowWidth="26080" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
   <si>
     <t>brand</t>
   </si>
@@ -254,9 +254,6 @@
     <t>gravel</t>
   </si>
   <si>
-    <t>flat bar</t>
-  </si>
-  <si>
     <t>a8:f32</t>
   </si>
   <si>
@@ -314,9 +311,6 @@
     <t>Fork Rake (mm)</t>
   </si>
   <si>
-    <t>titanium</t>
-  </si>
-  <si>
     <t>GBP</t>
   </si>
   <si>
@@ -327,6 +321,18 @@
   </si>
   <si>
     <t>SUPRACHUB</t>
+  </si>
+  <si>
+    <t>drop bar</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>integrated</t>
+  </si>
+  <si>
+    <t>steel</t>
   </si>
 </sst>
 </file>
@@ -691,7 +697,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -699,7 +705,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -723,7 +729,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -731,7 +737,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="22" x14ac:dyDescent="0.3">
@@ -739,16 +745,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" t="s">
         <v>77</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>78</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>79</v>
-      </c>
-      <c r="E8" t="s">
-        <v>80</v>
       </c>
       <c r="F8" t="s">
         <v>69</v>
@@ -764,7 +770,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9">
         <v>573</v>
@@ -785,7 +791,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10">
         <v>373</v>
@@ -806,7 +812,7 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11">
         <v>74</v>
@@ -827,7 +833,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12">
         <v>69</v>
@@ -848,7 +854,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13">
         <v>435</v>
@@ -869,7 +875,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14">
         <v>66</v>
@@ -894,7 +900,7 @@
         <v>71</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15">
         <v>82</v>
@@ -914,7 +920,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C16">
         <v>480</v>
@@ -935,7 +941,7 @@
         <v>10</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C17">
         <v>160</v>
@@ -956,7 +962,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C18">
         <v>540</v>
@@ -977,7 +983,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C19">
         <v>1059</v>
@@ -998,7 +1004,7 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C20">
         <v>55.5</v>
@@ -1094,7 +1100,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -1148,7 +1154,7 @@
         <v>67</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1164,14 +1170,16 @@
         <v>31</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="2"/>
+      <c r="B39" s="2" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -1235,7 +1243,7 @@
         <v>42</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -1289,7 +1297,9 @@
       <c r="A58" t="s">
         <v>51</v>
       </c>
-      <c r="B58" s="2"/>
+      <c r="B58" s="2" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
@@ -1375,7 +1385,7 @@
         <v>65</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Quirk SUPRACHUB 2025.xlsx
+++ b/data/gravel/Quirk SUPRACHUB 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB21CDAC-295E-4647-8FF2-D21332506096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305C36C0-228B-1148-8148-E669A82CA508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2720" yWindow="720" windowWidth="26080" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="102">
   <si>
     <t>brand</t>
   </si>
@@ -333,6 +333,12 @@
   </si>
   <si>
     <t>steel</t>
+  </si>
+  <si>
+    <t>https://images.squarespace-cdn.com/content/v1/55ec22b7e4b08b68bec3a4f6/1666342101308-MAFWM778RXM3BI6YCJT5/Quirk_Cycles_SUPRACHUB_04.jpg?format=1500w</t>
+  </si>
+  <si>
+    <t>Enve Adventure</t>
   </si>
 </sst>
 </file>
@@ -732,6 +738,11 @@
         <v>75</v>
       </c>
     </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+    </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
@@ -1034,6 +1045,21 @@
       <c r="A22" t="s">
         <v>21</v>
       </c>
+      <c r="C22" s="2">
+        <v>406</v>
+      </c>
+      <c r="D22" s="2">
+        <v>406</v>
+      </c>
+      <c r="E22" s="2">
+        <v>406</v>
+      </c>
+      <c r="F22" s="2">
+        <v>406</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>101</v>
+      </c>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">

--- a/data/gravel/Quirk SUPRACHUB 2025.xlsx
+++ b/data/gravel/Quirk SUPRACHUB 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305C36C0-228B-1148-8148-E669A82CA508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA762FB5-4728-C94E-B43C-4FA116365340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2720" yWindow="720" windowWidth="26080" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="104">
   <si>
     <t>brand</t>
   </si>
@@ -339,6 +339,12 @@
   </si>
   <si>
     <t>Enve Adventure</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>East London, UK</t>
   </si>
 </sst>
 </file>
@@ -692,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M72"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1414,6 +1420,14 @@
         <v>92</v>
       </c>
     </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>102</v>
+      </c>
+      <c r="B73" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Quirk SUPRACHUB 2025.xlsx
+++ b/data/gravel/Quirk SUPRACHUB 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA762FB5-4728-C94E-B43C-4FA116365340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8665343-C471-2C41-B593-EE24E3ED4343}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2720" yWindow="720" windowWidth="26080" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="110">
   <si>
     <t>brand</t>
   </si>
@@ -345,6 +345,24 @@
   </si>
   <si>
     <t>East London, UK</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -698,7 +716,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M73"/>
+  <dimension ref="A1:M79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1272,159 +1290,189 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>43</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>44</v>
-      </c>
-      <c r="B51">
-        <v>27.2</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>45</v>
-      </c>
-      <c r="B52" s="2"/>
+        <v>107</v>
+      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>49</v>
-      </c>
-      <c r="B56">
-        <v>160</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B57">
+        <v>27.2</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>51</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>98</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B58" s="2"/>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>52</v>
-      </c>
-      <c r="B59" s="2"/>
+        <v>46</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>53</v>
-      </c>
-      <c r="B60" s="2"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="B62">
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>57</v>
-      </c>
-      <c r="B64" s="2"/>
+        <v>51</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>58</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B65" s="2"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B66" s="2"/>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>60</v>
-      </c>
-      <c r="B67" s="2"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>61</v>
-      </c>
-      <c r="B68" s="2"/>
+        <v>55</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>62</v>
-      </c>
-      <c r="B69">
-        <v>4500</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>56</v>
+      </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>63</v>
-      </c>
-      <c r="B70">
-        <v>7000</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B70" s="2"/>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>64</v>
-      </c>
-      <c r="B71" s="2"/>
+        <v>58</v>
+      </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>65</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>92</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B72" s="2"/>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
+        <v>60</v>
+      </c>
+      <c r="B73" s="2"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B74" s="2"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75">
+        <v>4500</v>
+      </c>
+      <c r="C75" s="2"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>63</v>
+      </c>
+      <c r="B76">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B77" s="2"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>65</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>102</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B79" t="s">
         <v>103</v>
       </c>
     </row>
